--- a/src/results/TOC/optimized_results_TOC.xlsx
+++ b/src/results/TOC/optimized_results_TOC.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,6 +435,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
@@ -448,6 +453,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -457,9 +463,12 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.904</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>9.875</v>
+      </c>
+      <c r="D3" t="n">
+        <v>9.875</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -469,13 +478,16 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chrod length</t>
+          <t>Chord length</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -489,9 +501,12 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.841</v>
-      </c>
-      <c r="D5" t="inlineStr">
+        <v>0.855</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -505,9 +520,12 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>1.395</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -517,13 +535,16 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>battery energy density</t>
+          <t>Battery energy density</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>400</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>400</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Wh/kg</t>
         </is>
@@ -537,9 +558,12 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.029</v>
-      </c>
-      <c r="D8" t="inlineStr">
+        <v>2.021</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>1/h</t>
         </is>
@@ -554,6 +578,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -563,9 +588,12 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.904</v>
-      </c>
-      <c r="D10" t="inlineStr">
+        <v>9.875</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.875</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -581,7 +609,10 @@
       <c r="C11" t="n">
         <v>0.528</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -597,7 +628,10 @@
       <c r="C12" t="n">
         <v>0.051</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -611,9 +645,12 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.372</v>
-      </c>
-      <c r="D13" t="inlineStr">
+        <v>10.364</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10.364</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -627,9 +664,12 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1528.513</v>
-      </c>
-      <c r="D14" t="inlineStr">
+        <v>1531.623</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1531.623</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -645,7 +685,10 @@
       <c r="C15" t="n">
         <v>0.9350000000000001</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -661,7 +704,10 @@
       <c r="C16" t="n">
         <v>0.075</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -675,9 +721,12 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.496</v>
-      </c>
-      <c r="D17" t="inlineStr">
+        <v>12.479</v>
+      </c>
+      <c r="D17" t="n">
+        <v>12.479</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -691,9 +740,12 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1262.628</v>
-      </c>
-      <c r="D18" t="inlineStr">
+        <v>1265.955</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1265.955</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -708,6 +760,7 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -717,9 +770,12 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70.363</v>
-      </c>
-      <c r="D20" t="inlineStr">
+        <v>70.517</v>
+      </c>
+      <c r="D20" t="n">
+        <v>70.517</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -733,9 +789,12 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52.735</v>
-      </c>
-      <c r="D21" t="inlineStr">
+        <v>52.854</v>
+      </c>
+      <c r="D21" t="n">
+        <v>52.854</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -749,9 +808,12 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52.222</v>
-      </c>
-      <c r="D22" t="inlineStr">
+        <v>52.34</v>
+      </c>
+      <c r="D22" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -765,9 +827,12 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.339</v>
-      </c>
-      <c r="D23" t="inlineStr">
+        <v>7.356</v>
+      </c>
+      <c r="D23" t="n">
+        <v>7.356</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -782,6 +847,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -791,9 +857,12 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3480.136</v>
-      </c>
-      <c r="D25" t="inlineStr">
+        <v>3486.282</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3486.282</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -807,9 +876,12 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3480.136</v>
-      </c>
-      <c r="D26" t="inlineStr">
+        <v>3486.282</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3486.282</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -823,9 +895,12 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>286126.814</v>
-      </c>
-      <c r="D27" t="inlineStr">
+        <v>285905.978</v>
+      </c>
+      <c r="D27" t="n">
+        <v>285905.978</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -839,9 +914,12 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>286126.814</v>
-      </c>
-      <c r="D28" t="inlineStr">
+        <v>285905.978</v>
+      </c>
+      <c r="D28" t="n">
+        <v>285905.978</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -855,9 +933,12 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1530.611</v>
-      </c>
-      <c r="D29" t="inlineStr">
+        <v>1533.725</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1533.725</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -871,9 +952,12 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1530.611</v>
-      </c>
-      <c r="D30" t="inlineStr">
+        <v>1533.725</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1533.725</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -887,9 +971,12 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>148366.903</v>
-      </c>
-      <c r="D31" t="inlineStr">
+        <v>148748.25</v>
+      </c>
+      <c r="D31" t="n">
+        <v>148748.25</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -903,9 +990,12 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>148366.903</v>
-      </c>
-      <c r="D32" t="inlineStr">
+        <v>148748.25</v>
+      </c>
+      <c r="D32" t="n">
+        <v>148748.25</v>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -919,9 +1009,12 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15933.449</v>
-      </c>
-      <c r="D33" t="inlineStr">
+        <v>15953.71</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15953.71</v>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -935,9 +1028,12 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1991.681</v>
-      </c>
-      <c r="D34" t="inlineStr">
+        <v>1994.214</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1994.214</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -951,9 +1047,12 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>290644.811</v>
-      </c>
-      <c r="D35" t="inlineStr">
+        <v>292179.081</v>
+      </c>
+      <c r="D35" t="n">
+        <v>292179.081</v>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -967,9 +1066,12 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36330.601</v>
-      </c>
-      <c r="D36" t="inlineStr">
+        <v>36522.385</v>
+      </c>
+      <c r="D36" t="n">
+        <v>36522.385</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -983,9 +1085,12 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>323.558</v>
-      </c>
-      <c r="D37" t="inlineStr">
+        <v>326.154</v>
+      </c>
+      <c r="D37" t="n">
+        <v>326.154</v>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>N/m²</t>
         </is>
@@ -1000,6 +1105,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -1009,9 +1115,12 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.734</v>
-      </c>
-      <c r="D39" t="inlineStr">
+        <v>2.728</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.728</v>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -1025,9 +1134,12 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14.551</v>
-      </c>
-      <c r="D40" t="inlineStr">
+        <v>14.52</v>
+      </c>
+      <c r="D40" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -1041,9 +1153,12 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18.285</v>
-      </c>
-      <c r="D41" t="inlineStr">
+        <v>18.248</v>
+      </c>
+      <c r="D41" t="n">
+        <v>18.248</v>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -1058,6 +1173,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -1067,9 +1183,12 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4844.08</v>
-      </c>
-      <c r="D43" t="inlineStr">
+        <v>4869.651</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4869.651</v>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1083,9 +1202,12 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13037.992</v>
-      </c>
-      <c r="D44" t="inlineStr">
+        <v>12998.706</v>
+      </c>
+      <c r="D44" t="n">
+        <v>12998.706</v>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1099,9 +1221,12 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35982.527</v>
-      </c>
-      <c r="D45" t="inlineStr">
+        <v>35996.415</v>
+      </c>
+      <c r="D45" t="n">
+        <v>35996.415</v>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1115,9 +1240,12 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>53864.599</v>
-      </c>
-      <c r="D46" t="inlineStr">
+        <v>53864.773</v>
+      </c>
+      <c r="D46" t="n">
+        <v>53864.773</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1131,9 +1259,12 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49455.634</v>
-      </c>
-      <c r="D47" t="inlineStr">
+        <v>49582.75</v>
+      </c>
+      <c r="D47" t="n">
+        <v>49582.75</v>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1147,9 +1278,12 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>103320.233</v>
-      </c>
-      <c r="D48" t="inlineStr">
+        <v>103447.522</v>
+      </c>
+      <c r="D48" t="n">
+        <v>103447.522</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1163,9 +1297,12 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>161437.865</v>
-      </c>
-      <c r="D49" t="inlineStr">
+        <v>161636.754</v>
+      </c>
+      <c r="D49" t="n">
+        <v>161636.754</v>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1179,9 +1316,12 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>58117.631</v>
-      </c>
-      <c r="D50" t="inlineStr">
+        <v>58189.231</v>
+      </c>
+      <c r="D50" t="n">
+        <v>58189.231</v>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>Wh</t>
         </is>
@@ -1196,6 +1336,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -1205,9 +1346,12 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>13.125</v>
-      </c>
-      <c r="D52" t="inlineStr">
+        <v>13.092</v>
+      </c>
+      <c r="D52" t="n">
+        <v>13.092</v>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1221,9 +1365,12 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.595</v>
-      </c>
-      <c r="D53" t="inlineStr">
+        <v>54.679</v>
+      </c>
+      <c r="D53" t="n">
+        <v>54.679</v>
+      </c>
+      <c r="E53" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1237,9 +1384,12 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>43.398</v>
-      </c>
-      <c r="D54" t="inlineStr">
+        <v>44.519</v>
+      </c>
+      <c r="D54" t="n">
+        <v>44.519</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1253,9 +1403,12 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>113.813</v>
-      </c>
-      <c r="D55" t="inlineStr">
+        <v>114.025</v>
+      </c>
+      <c r="D55" t="n">
+        <v>114.025</v>
+      </c>
+      <c r="E55" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1269,9 +1422,12 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>253.557</v>
-      </c>
-      <c r="D56" t="inlineStr">
+        <v>254.141</v>
+      </c>
+      <c r="D56" t="n">
+        <v>254.141</v>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1285,9 +1441,12 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>118.128</v>
-      </c>
-      <c r="D57" t="inlineStr">
+        <v>117.825</v>
+      </c>
+      <c r="D57" t="n">
+        <v>117.825</v>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1301,9 +1460,12 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>80.789</v>
-      </c>
-      <c r="D58" t="inlineStr">
+        <v>80.855</v>
+      </c>
+      <c r="D58" t="n">
+        <v>80.855</v>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1317,9 +1479,12 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>67.03100000000001</v>
-      </c>
-      <c r="D59" t="inlineStr">
+        <v>66.83499999999999</v>
+      </c>
+      <c r="D59" t="n">
+        <v>66.83499999999999</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1335,7 +1500,10 @@
       <c r="C60" t="n">
         <v>392.8</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1351,7 +1519,10 @@
       <c r="C61" t="n">
         <v>96.5</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1365,9 +1536,12 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>403.595</v>
-      </c>
-      <c r="D62" t="inlineStr">
+        <v>404.092</v>
+      </c>
+      <c r="D62" t="n">
+        <v>404.092</v>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1381,9 +1555,12 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>827.8099999999999</v>
-      </c>
-      <c r="D63" t="inlineStr">
+        <v>829.378</v>
+      </c>
+      <c r="D63" t="n">
+        <v>829.378</v>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1397,9 +1574,12 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1624.205</v>
-      </c>
-      <c r="D64" t="inlineStr">
+        <v>1626.27</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1626.27</v>
+      </c>
+      <c r="E64" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1413,9 +1593,12 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1624.205</v>
-      </c>
-      <c r="D65" t="inlineStr">
+        <v>1626.27</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1626.27</v>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -1431,7 +1614,10 @@
       <c r="C66" t="n">
         <v>0.248</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1447,7 +1633,10 @@
       <c r="C67" t="n">
         <v>0.51</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1462,6 +1651,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -1471,9 +1661,12 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="D69" t="inlineStr">
+        <v>0.888</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1487,9 +1680,12 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2369.868</v>
-      </c>
-      <c r="D70" t="inlineStr">
+        <v>2297.492</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2297.492</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
@@ -1503,9 +1699,12 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>27.871</v>
-      </c>
-      <c r="D71" t="inlineStr">
+        <v>27.321</v>
+      </c>
+      <c r="D71" t="n">
+        <v>27.321</v>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>dB</t>
         </is>
@@ -1519,9 +1718,12 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3573.468</v>
-      </c>
-      <c r="D72" t="inlineStr">
+        <v>3463.87</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3463.87</v>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
@@ -1535,9 +1737,12 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50.718</v>
-      </c>
-      <c r="D73" t="inlineStr">
+        <v>50.16</v>
+      </c>
+      <c r="D73" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>dB</t>
         </is>
@@ -1551,9 +1756,12 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>976.149</v>
-      </c>
-      <c r="D74" t="inlineStr">
+        <v>983.353</v>
+      </c>
+      <c r="D74" t="n">
+        <v>983.353</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>RPM</t>
         </is>
@@ -1567,9 +1775,12 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74.44</v>
-      </c>
-      <c r="D75" t="inlineStr">
+        <v>74.577</v>
+      </c>
+      <c r="D75" t="n">
+        <v>74.577</v>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>dB</t>
         </is>
@@ -1584,6 +1795,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -1593,9 +1805,12 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D77" t="inlineStr">
+        <v>1.808</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1.808</v>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>1/h</t>
         </is>
@@ -1609,9 +1824,12 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.772</v>
-      </c>
-      <c r="D78" t="inlineStr">
+        <v>1.769</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.769</v>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>1/h</t>
         </is>
@@ -1625,9 +1843,12 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="D79" t="inlineStr">
+        <v>0.92</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>1/h</t>
         </is>
@@ -1641,9 +1862,12 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.095</v>
-      </c>
-      <c r="D80" t="inlineStr">
+        <v>1.096</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>1/h</t>
         </is>
@@ -1657,9 +1881,12 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="D81" t="inlineStr">
+        <v>0.333</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1673,9 +1900,12 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1893.618</v>
-      </c>
-      <c r="D82" t="inlineStr">
+        <v>1901.088</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1901.088</v>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1689,9 +1919,12 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2.341</v>
-      </c>
-      <c r="D83" t="inlineStr">
+        <v>2.333</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1706,6 +1939,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -1715,9 +1949,12 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9.868</v>
-      </c>
-      <c r="D85" t="inlineStr">
+        <v>9.893000000000001</v>
+      </c>
+      <c r="D85" t="n">
+        <v>9.893000000000001</v>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -1731,9 +1968,12 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>28.153</v>
-      </c>
-      <c r="D86" t="inlineStr">
+        <v>28.141</v>
+      </c>
+      <c r="D86" t="n">
+        <v>28.141</v>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>min</t>
         </is>
@@ -1747,9 +1987,12 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="D87" t="inlineStr">
+        <v>1.542</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1763,9 +2006,12 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="D88" t="inlineStr">
+        <v>17.057</v>
+      </c>
+      <c r="D88" t="n">
+        <v>17.057</v>
+      </c>
+      <c r="E88" t="inlineStr">
         <is>
           <t>flights</t>
         </is>
@@ -1779,9 +2025,12 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.196</v>
-      </c>
-      <c r="D89" t="inlineStr">
+        <v>5.187</v>
+      </c>
+      <c r="D89" t="n">
+        <v>5.187</v>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
@@ -1795,9 +2044,12 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4432.907</v>
-      </c>
-      <c r="D90" t="inlineStr">
+        <v>4434.794</v>
+      </c>
+      <c r="D90" t="n">
+        <v>4434.794</v>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>flights</t>
         </is>
@@ -1811,9 +2063,12 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1350.963</v>
-      </c>
-      <c r="D91" t="inlineStr">
+        <v>1348.741</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1348.741</v>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>hours</t>
         </is>
@@ -1828,6 +2083,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -1837,9 +2093,12 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>20099.014</v>
-      </c>
-      <c r="D93" t="inlineStr">
+        <v>20123.776</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20123.776</v>
+      </c>
+      <c r="E93" t="inlineStr">
         <is>
           <t>kg CO2e</t>
         </is>
@@ -1853,9 +2112,12 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47051.235</v>
-      </c>
-      <c r="D94" t="inlineStr">
+        <v>46944.052</v>
+      </c>
+      <c r="D94" t="n">
+        <v>46944.052</v>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>kg CO2e</t>
         </is>
@@ -1869,9 +2131,12 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10.614</v>
-      </c>
-      <c r="D95" t="inlineStr">
+        <v>10.585</v>
+      </c>
+      <c r="D95" t="n">
+        <v>10.585</v>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>kg CO2e</t>
         </is>
@@ -1887,7 +2152,10 @@
       <c r="C96" t="n">
         <v>20.413</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" t="n">
+        <v>20.413</v>
+      </c>
+      <c r="E96" t="inlineStr">
         <is>
           <t>kg CO2e</t>
         </is>
@@ -1901,9 +2169,12 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>31.027</v>
-      </c>
-      <c r="D97" t="inlineStr">
+        <v>30.998</v>
+      </c>
+      <c r="D97" t="n">
+        <v>30.998</v>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>kg CO2e</t>
         </is>
@@ -1917,9 +2188,12 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>137538.08</v>
-      </c>
-      <c r="D98" t="inlineStr">
+        <v>137469.698</v>
+      </c>
+      <c r="D98" t="n">
+        <v>137469.698</v>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>kg CO2e</t>
         </is>
@@ -1933,9 +2207,12 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="D99" t="inlineStr">
+        <v>65.851</v>
+      </c>
+      <c r="D99" t="n">
+        <v>65.851</v>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1949,9 +2226,12 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>34.21</v>
-      </c>
-      <c r="D100" t="inlineStr">
+        <v>34.149</v>
+      </c>
+      <c r="D100" t="n">
+        <v>34.149</v>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1966,6 +2246,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -1977,7 +2258,10 @@
       <c r="C102" t="n">
         <v>5.207</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" t="n">
+        <v>5.207</v>
+      </c>
+      <c r="E102" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -1991,9 +2275,12 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17.389</v>
-      </c>
-      <c r="D103" t="inlineStr">
+        <v>17.402</v>
+      </c>
+      <c r="D103" t="n">
+        <v>17.402</v>
+      </c>
+      <c r="E103" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2007,9 +2294,12 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.628</v>
-      </c>
-      <c r="D104" t="inlineStr">
+        <v>10.623</v>
+      </c>
+      <c r="D104" t="n">
+        <v>10.623</v>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2023,9 +2313,12 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10.057</v>
-      </c>
-      <c r="D105" t="inlineStr">
+        <v>10.036</v>
+      </c>
+      <c r="D105" t="n">
+        <v>10.036</v>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2039,9 +2332,12 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>18565.354</v>
-      </c>
-      <c r="D106" t="inlineStr">
+        <v>18588.227</v>
+      </c>
+      <c r="D106" t="n">
+        <v>18588.227</v>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2055,9 +2351,12 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9.804</v>
-      </c>
-      <c r="D107" t="inlineStr">
+        <v>9.778</v>
+      </c>
+      <c r="D107" t="n">
+        <v>9.778</v>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2071,9 +2370,12 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>19.861</v>
-      </c>
-      <c r="D108" t="inlineStr">
+        <v>19.814</v>
+      </c>
+      <c r="D108" t="n">
+        <v>19.814</v>
+      </c>
+      <c r="E108" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2087,9 +2389,12 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>53.085</v>
-      </c>
-      <c r="D109" t="inlineStr">
+        <v>53.046</v>
+      </c>
+      <c r="D109" t="n">
+        <v>53.046</v>
+      </c>
+      <c r="E109" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2103,9 +2408,12 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>24.538</v>
-      </c>
-      <c r="D110" t="inlineStr">
+        <v>24.567</v>
+      </c>
+      <c r="D110" t="n">
+        <v>24.567</v>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2119,9 +2427,12 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>77.623</v>
-      </c>
-      <c r="D111" t="inlineStr">
+        <v>77.613</v>
+      </c>
+      <c r="D111" t="n">
+        <v>77.613</v>
+      </c>
+      <c r="E111" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2135,9 +2446,12 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>17.063</v>
-      </c>
-      <c r="D112" t="inlineStr">
+        <v>17.061</v>
+      </c>
+      <c r="D112" t="n">
+        <v>17.061</v>
+      </c>
+      <c r="E112" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2151,9 +2465,12 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>94.68600000000001</v>
-      </c>
-      <c r="D113" t="inlineStr">
+        <v>94.67400000000001</v>
+      </c>
+      <c r="D113" t="n">
+        <v>94.67400000000001</v>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2169,7 +2486,10 @@
       <c r="C114" t="n">
         <v>0.338</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>€/km</t>
         </is>
@@ -2183,9 +2503,12 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.295</v>
-      </c>
-      <c r="D115" t="inlineStr">
+        <v>1.297</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1.297</v>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t>€/min</t>
         </is>
@@ -2200,6 +2523,7 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -2211,7 +2535,10 @@
       <c r="C117" t="n">
         <v>138.6</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" t="n">
+        <v>138.6</v>
+      </c>
+      <c r="E117" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2227,7 +2554,10 @@
       <c r="C118" t="n">
         <v>376.992</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" t="n">
+        <v>376.992</v>
+      </c>
+      <c r="E118" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2242,6 +2572,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -2251,9 +2582,12 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>282.306</v>
-      </c>
-      <c r="D120" t="inlineStr">
+        <v>282.318</v>
+      </c>
+      <c r="D120" t="n">
+        <v>282.318</v>
+      </c>
+      <c r="E120" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2267,9 +2601,12 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1251435.402</v>
-      </c>
-      <c r="D121" t="inlineStr">
+        <v>1252021.507</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1252021.507</v>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2354,7 +2691,7 @@
         <v>64.235</v>
       </c>
       <c r="D2" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1.183</v>
@@ -2388,7 +2725,7 @@
         <v>64.235</v>
       </c>
       <c r="D3" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>2.366</v>
@@ -2422,7 +2759,7 @@
         <v>50.909</v>
       </c>
       <c r="D4" t="n">
-        <v>8.903</v>
+        <v>8.901999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.588</v>
@@ -2456,7 +2793,7 @@
         <v>64.235</v>
       </c>
       <c r="D5" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>2.821</v>
@@ -2558,7 +2895,7 @@
         <v>64.235</v>
       </c>
       <c r="D8" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E8" t="n">
         <v>4.55</v>
@@ -2592,7 +2929,7 @@
         <v>50.909</v>
       </c>
       <c r="D9" t="n">
-        <v>8.903</v>
+        <v>8.901999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>1.008</v>
@@ -2654,13 +2991,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.659</v>
+        <v>6.658</v>
       </c>
       <c r="C11" t="n">
         <v>64.235</v>
       </c>
       <c r="D11" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>5.915</v>
@@ -2688,13 +3025,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.281</v>
+        <v>6.28</v>
       </c>
       <c r="C12" t="n">
         <v>64.235</v>
       </c>
       <c r="D12" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>9.009</v>
@@ -2722,13 +3059,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.886</v>
+        <v>5.885</v>
       </c>
       <c r="C13" t="n">
         <v>64.235</v>
       </c>
       <c r="D13" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>10.92</v>
@@ -2762,7 +3099,7 @@
         <v>64.235</v>
       </c>
       <c r="D14" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>11.648</v>
@@ -2790,31 +3127,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.398</v>
+        <v>5.4</v>
       </c>
       <c r="C15" t="n">
-        <v>18.285</v>
+        <v>18.248</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>11.407</v>
+        <v>11.396</v>
       </c>
       <c r="F15" t="n">
-        <v>4.391</v>
+        <v>4.396</v>
       </c>
       <c r="G15" t="n">
-        <v>19803.161</v>
+        <v>19803.225</v>
       </c>
       <c r="H15" t="n">
         <v>6.032</v>
       </c>
       <c r="I15" t="n">
-        <v>34.811</v>
+        <v>34.807</v>
       </c>
       <c r="J15" t="n">
-        <v>1.805</v>
+        <v>1.806</v>
       </c>
     </row>
     <row r="16">
@@ -2824,13 +3161,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.249</v>
+        <v>5.248</v>
       </c>
       <c r="C16" t="n">
         <v>64.235</v>
       </c>
       <c r="D16" t="n">
-        <v>8.455</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>14.287</v>

--- a/src/results/TOC/optimized_results_TOC.xlsx
+++ b/src/results/TOC/optimized_results_TOC.xlsx
@@ -463,10 +463,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.875</v>
+        <v>11.895</v>
       </c>
       <c r="D3" t="n">
-        <v>9.875</v>
+        <v>9.874000000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.855</v>
+        <v>1.002</v>
       </c>
       <c r="D5" t="n">
-        <v>0.855</v>
+        <v>0.856</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.395</v>
+        <v>1.687</v>
       </c>
       <c r="D6" t="n">
         <v>1.395</v>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.021</v>
+        <v>2.006</v>
       </c>
       <c r="D8" t="n">
-        <v>2.021</v>
+        <v>2.025</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.875</v>
+        <v>11.895</v>
       </c>
       <c r="D10" t="n">
-        <v>9.875</v>
+        <v>9.874000000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.528</v>
+        <v>0.536</v>
       </c>
       <c r="D11" t="n">
         <v>0.528</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="D12" t="n">
         <v>0.051</v>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.364</v>
+        <v>10.867</v>
       </c>
       <c r="D13" t="n">
         <v>10.364</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1531.623</v>
+        <v>1752.916</v>
       </c>
       <c r="D14" t="n">
-        <v>1531.623</v>
+        <v>1531.77</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.956</v>
       </c>
       <c r="D15" t="n">
         <v>0.9350000000000001</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>0.075</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.479</v>
+        <v>13.605</v>
       </c>
       <c r="D17" t="n">
         <v>12.479</v>
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1265.955</v>
+        <v>1393.237</v>
       </c>
       <c r="D18" t="n">
-        <v>1265.955</v>
+        <v>1266.105</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70.517</v>
+        <v>69.858</v>
       </c>
       <c r="D20" t="n">
-        <v>70.517</v>
+        <v>70.524</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52.854</v>
+        <v>52.156</v>
       </c>
       <c r="D21" t="n">
-        <v>52.854</v>
+        <v>52.859</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52.34</v>
+        <v>51.648</v>
       </c>
       <c r="D22" t="n">
-        <v>52.34</v>
+        <v>52.344</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.356</v>
+        <v>7.259</v>
       </c>
       <c r="D23" t="n">
-        <v>7.356</v>
+        <v>7.357</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3486.282</v>
+        <v>4057.212</v>
       </c>
       <c r="D25" t="n">
-        <v>3486.282</v>
+        <v>3486.582</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3486.282</v>
+        <v>4057.212</v>
       </c>
       <c r="D26" t="n">
-        <v>3486.282</v>
+        <v>3486.582</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>285905.978</v>
+        <v>322427.265</v>
       </c>
       <c r="D27" t="n">
-        <v>285905.978</v>
+        <v>285824.324</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>285905.978</v>
+        <v>322427.265</v>
       </c>
       <c r="D28" t="n">
-        <v>285905.978</v>
+        <v>285824.324</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1533.725</v>
+        <v>1755.321</v>
       </c>
       <c r="D29" t="n">
-        <v>1533.725</v>
+        <v>1533.872</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1533.725</v>
+        <v>1755.321</v>
       </c>
       <c r="D30" t="n">
-        <v>1533.725</v>
+        <v>1533.872</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>148748.25</v>
+        <v>167436.031</v>
       </c>
       <c r="D31" t="n">
-        <v>148748.25</v>
+        <v>148752.248</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>148748.25</v>
+        <v>167436.031</v>
       </c>
       <c r="D32" t="n">
-        <v>148748.25</v>
+        <v>148752.248</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15953.71</v>
+        <v>19141.451</v>
       </c>
       <c r="D33" t="n">
-        <v>15953.71</v>
+        <v>15954.791</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1994.214</v>
+        <v>2392.681</v>
       </c>
       <c r="D34" t="n">
-        <v>1994.214</v>
+        <v>1994.349</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>292179.081</v>
+        <v>317567.349</v>
       </c>
       <c r="D35" t="n">
-        <v>292179.081</v>
+        <v>292245.381</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36522.385</v>
+        <v>39695.919</v>
       </c>
       <c r="D36" t="n">
-        <v>36522.385</v>
+        <v>36530.673</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>326.154</v>
+        <v>267.651</v>
       </c>
       <c r="D37" t="n">
-        <v>326.154</v>
+        <v>326.257</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.728</v>
+        <v>2.764</v>
       </c>
       <c r="D39" t="n">
         <v>2.728</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14.52</v>
+        <v>14.657</v>
       </c>
       <c r="D40" t="n">
-        <v>14.52</v>
+        <v>14.518</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18.248</v>
+        <v>18.421</v>
       </c>
       <c r="D41" t="n">
-        <v>18.248</v>
+        <v>18.246</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4869.651</v>
+        <v>5292.789</v>
       </c>
       <c r="D43" t="n">
-        <v>4869.651</v>
+        <v>4870.756</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12998.706</v>
+        <v>14855.325</v>
       </c>
       <c r="D44" t="n">
-        <v>12998.706</v>
+        <v>12993.774</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35996.415</v>
+        <v>40901.202</v>
       </c>
       <c r="D45" t="n">
-        <v>35996.415</v>
+        <v>35994.088</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>53864.773</v>
+        <v>61049.315</v>
       </c>
       <c r="D46" t="n">
-        <v>53864.773</v>
+        <v>53858.618</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49582.75</v>
+        <v>55812.01</v>
       </c>
       <c r="D47" t="n">
-        <v>49582.75</v>
+        <v>49584.083</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>103447.522</v>
+        <v>116861.326</v>
       </c>
       <c r="D48" t="n">
-        <v>103447.522</v>
+        <v>103442.701</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>161636.754</v>
+        <v>182595.821</v>
       </c>
       <c r="D49" t="n">
-        <v>161636.754</v>
+        <v>161629.221</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>58189.231</v>
+        <v>65734.496</v>
       </c>
       <c r="D50" t="n">
-        <v>58189.231</v>
+        <v>58186.519</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>13.092</v>
+        <v>16.436</v>
       </c>
       <c r="D52" t="n">
         <v>13.092</v>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.679</v>
+        <v>64.03100000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>54.679</v>
+        <v>54.683</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44.519</v>
+        <v>62.737</v>
       </c>
       <c r="D54" t="n">
-        <v>44.519</v>
+        <v>44.632</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>114.025</v>
+        <v>117.888</v>
       </c>
       <c r="D55" t="n">
-        <v>114.025</v>
+        <v>114.034</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1422,10 +1422,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>254.141</v>
+        <v>274.335</v>
       </c>
       <c r="D56" t="n">
-        <v>254.141</v>
+        <v>254.147</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>117.825</v>
+        <v>147.925</v>
       </c>
       <c r="D57" t="n">
-        <v>117.825</v>
+        <v>117.824</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>80.855</v>
+        <v>92.42</v>
       </c>
       <c r="D58" t="n">
-        <v>80.855</v>
+        <v>80.85899999999999</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>66.83499999999999</v>
+        <v>93.929</v>
       </c>
       <c r="D59" t="n">
-        <v>66.83499999999999</v>
+        <v>66.828</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>404.092</v>
+        <v>608.653</v>
       </c>
       <c r="D62" t="n">
-        <v>404.092</v>
+        <v>404.073</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>829.378</v>
+        <v>949.765</v>
       </c>
       <c r="D63" t="n">
-        <v>829.378</v>
+        <v>829.5069999999999</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1626.27</v>
+        <v>1951.218</v>
       </c>
       <c r="D64" t="n">
-        <v>1626.27</v>
+        <v>1626.38</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1626.27</v>
+        <v>1951.218</v>
       </c>
       <c r="D65" t="n">
-        <v>1626.27</v>
+        <v>1626.38</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.248</v>
+        <v>0.312</v>
       </c>
       <c r="D66" t="n">
         <v>0.248</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.51</v>
+        <v>0.487</v>
       </c>
       <c r="D67" t="n">
         <v>0.51</v>
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.888</v>
+        <v>0.772</v>
       </c>
       <c r="D69" t="n">
-        <v>0.888</v>
+        <v>0.885</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2297.492</v>
+        <v>1788.975</v>
       </c>
       <c r="D70" t="n">
-        <v>2297.492</v>
+        <v>2289.977</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>27.321</v>
+        <v>24.896</v>
       </c>
       <c r="D71" t="n">
-        <v>27.321</v>
+        <v>27.264</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3463.87</v>
+        <v>2719.817</v>
       </c>
       <c r="D72" t="n">
-        <v>3463.87</v>
+        <v>3452.523</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50.16</v>
+        <v>48.166</v>
       </c>
       <c r="D73" t="n">
-        <v>50.16</v>
+        <v>50.103</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>983.353</v>
+        <v>736.716</v>
       </c>
       <c r="D74" t="n">
-        <v>983.353</v>
+        <v>983.6319999999999</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>74.577</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>74.577</v>
+        <v>74.583</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.808</v>
+        <v>1.739</v>
       </c>
       <c r="D77" t="n">
         <v>1.808</v>
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.769</v>
+        <v>1.766</v>
       </c>
       <c r="D78" t="n">
-        <v>1.769</v>
+        <v>1.768</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.92</v>
+        <v>0.917</v>
       </c>
       <c r="D79" t="n">
         <v>0.92</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.096</v>
+        <v>1.089</v>
       </c>
       <c r="D80" t="n">
         <v>1.096</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="D81" t="n">
         <v>0.333</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1901.088</v>
+        <v>1930.165</v>
       </c>
       <c r="D82" t="n">
-        <v>1901.088</v>
+        <v>1896.176</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2.333</v>
+        <v>2.275</v>
       </c>
       <c r="D83" t="n">
-        <v>2.333</v>
+        <v>2.341</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9.893000000000001</v>
+        <v>10.001</v>
       </c>
       <c r="D85" t="n">
-        <v>9.893000000000001</v>
+        <v>9.872</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>28.141</v>
+        <v>28.422</v>
       </c>
       <c r="D86" t="n">
-        <v>28.141</v>
+        <v>28.118</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.542</v>
+        <v>1.543</v>
       </c>
       <c r="D87" t="n">
-        <v>1.542</v>
+        <v>1.541</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>17.057</v>
+        <v>16.888</v>
       </c>
       <c r="D88" t="n">
-        <v>17.057</v>
+        <v>17.071</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.187</v>
+        <v>5.185</v>
       </c>
       <c r="D89" t="n">
-        <v>5.187</v>
+        <v>5.191</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4434.794</v>
+        <v>4390.919</v>
       </c>
       <c r="D90" t="n">
-        <v>4434.794</v>
+        <v>4438.501</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1348.741</v>
+        <v>1348.098</v>
       </c>
       <c r="D91" t="n">
-        <v>1348.741</v>
+        <v>1349.751</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2093,10 +2093,10 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>20123.776</v>
+        <v>22733.18</v>
       </c>
       <c r="D93" t="n">
-        <v>20123.776</v>
+        <v>20122.838</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>46944.052</v>
+        <v>51715.546</v>
       </c>
       <c r="D94" t="n">
-        <v>46944.052</v>
+        <v>47102.821</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10.585</v>
+        <v>11.778</v>
       </c>
       <c r="D95" t="n">
-        <v>10.585</v>
+        <v>10.612</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20.413</v>
+        <v>23.135</v>
       </c>
       <c r="D96" t="n">
-        <v>20.413</v>
+        <v>20.41</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>30.998</v>
+        <v>34.913</v>
       </c>
       <c r="D97" t="n">
-        <v>30.998</v>
+        <v>31.023</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>137469.698</v>
+        <v>153300.553</v>
       </c>
       <c r="D98" t="n">
-        <v>137469.698</v>
+        <v>137693.781</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>65.851</v>
+        <v>66.265</v>
       </c>
       <c r="D99" t="n">
-        <v>65.851</v>
+        <v>65.792</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>34.149</v>
+        <v>33.735</v>
       </c>
       <c r="D100" t="n">
-        <v>34.149</v>
+        <v>34.208</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5.207</v>
+        <v>5.902</v>
       </c>
       <c r="D102" t="n">
-        <v>5.207</v>
+        <v>5.206</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17.402</v>
+        <v>19.357</v>
       </c>
       <c r="D103" t="n">
         <v>17.402</v>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.623</v>
+        <v>10.729</v>
       </c>
       <c r="D104" t="n">
-        <v>10.623</v>
+        <v>10.614</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10.036</v>
+        <v>10.132</v>
       </c>
       <c r="D105" t="n">
-        <v>10.036</v>
+        <v>10.035</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>18588.227</v>
+        <v>20998.519</v>
       </c>
       <c r="D106" t="n">
-        <v>18588.227</v>
+        <v>18587.36</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9.778</v>
+        <v>10.879</v>
       </c>
       <c r="D107" t="n">
-        <v>9.778</v>
+        <v>9.803000000000001</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>19.814</v>
+        <v>21.011</v>
       </c>
       <c r="D108" t="n">
-        <v>19.814</v>
+        <v>19.838</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>53.046</v>
+        <v>56.999</v>
       </c>
       <c r="D109" t="n">
-        <v>53.046</v>
+        <v>53.061</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>24.567</v>
+        <v>28.153</v>
       </c>
       <c r="D110" t="n">
-        <v>24.567</v>
+        <v>24.554</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>77.613</v>
+        <v>85.152</v>
       </c>
       <c r="D111" t="n">
-        <v>77.613</v>
+        <v>77.61499999999999</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>17.061</v>
+        <v>18.718</v>
       </c>
       <c r="D112" t="n">
         <v>17.061</v>
@@ -2465,10 +2465,10 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>94.67400000000001</v>
+        <v>103.87</v>
       </c>
       <c r="D113" t="n">
-        <v>94.67400000000001</v>
+        <v>94.676</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.338</v>
+        <v>0.371</v>
       </c>
       <c r="D114" t="n">
         <v>0.338</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.297</v>
+        <v>1.41</v>
       </c>
       <c r="D115" t="n">
         <v>1.297</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>282.318</v>
+        <v>273.122</v>
       </c>
       <c r="D120" t="n">
-        <v>282.318</v>
+        <v>282.316</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1252021.507</v>
+        <v>1199255.011</v>
       </c>
       <c r="D121" t="n">
-        <v>1252021.507</v>
+        <v>1253059.328</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.699</v>
+        <v>7.7</v>
       </c>
       <c r="C2" t="n">
         <v>64.235</v>
       </c>
       <c r="D2" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E2" t="n">
         <v>1.183</v>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.518</v>
+        <v>7.519</v>
       </c>
       <c r="C3" t="n">
         <v>64.235</v>
       </c>
       <c r="D3" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E3" t="n">
         <v>2.366</v>
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.43</v>
+        <v>7.431</v>
       </c>
       <c r="C4" t="n">
         <v>50.909</v>
       </c>
       <c r="D4" t="n">
-        <v>8.901999999999999</v>
+        <v>8.907</v>
       </c>
       <c r="E4" t="n">
         <v>0.588</v>
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.424</v>
+        <v>7.426</v>
       </c>
       <c r="C5" t="n">
         <v>64.235</v>
       </c>
       <c r="D5" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E5" t="n">
         <v>2.821</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.031</v>
+        <v>7.032</v>
       </c>
       <c r="C6" t="n">
         <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>7.084</v>
+        <v>7.087</v>
       </c>
       <c r="E6" t="n">
         <v>1.456</v>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.958</v>
+        <v>6.959</v>
       </c>
       <c r="C8" t="n">
         <v>64.235</v>
       </c>
       <c r="D8" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E8" t="n">
         <v>4.55</v>
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.773</v>
+        <v>6.774</v>
       </c>
       <c r="C9" t="n">
         <v>50.909</v>
       </c>
       <c r="D9" t="n">
-        <v>8.901999999999999</v>
+        <v>8.907</v>
       </c>
       <c r="E9" t="n">
         <v>1.008</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.695</v>
+        <v>6.696</v>
       </c>
       <c r="C10" t="n">
         <v>105</v>
       </c>
       <c r="D10" t="n">
-        <v>7.084</v>
+        <v>7.087</v>
       </c>
       <c r="E10" t="n">
         <v>2.464</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.658</v>
+        <v>6.66</v>
       </c>
       <c r="C11" t="n">
         <v>64.235</v>
       </c>
       <c r="D11" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E11" t="n">
         <v>5.915</v>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.28</v>
+        <v>6.282</v>
       </c>
       <c r="C12" t="n">
         <v>64.235</v>
       </c>
       <c r="D12" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E12" t="n">
         <v>9.009</v>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.885</v>
+        <v>5.887</v>
       </c>
       <c r="C13" t="n">
         <v>64.235</v>
       </c>
       <c r="D13" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E13" t="n">
         <v>10.92</v>
@@ -3093,13 +3093,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.788</v>
+        <v>5.79</v>
       </c>
       <c r="C14" t="n">
         <v>64.235</v>
       </c>
       <c r="D14" t="n">
-        <v>8.454000000000001</v>
+        <v>8.459</v>
       </c>
       <c r="E14" t="n">
         <v>11.648</v>
@@ -3123,69 +3123,69 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>eVTOL</t>
+          <t>Gasonline Vehicle (20%)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="C15" t="n">
-        <v>18.248</v>
+        <v>64.235</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>8.459</v>
       </c>
       <c r="E15" t="n">
-        <v>11.396</v>
+        <v>14.287</v>
       </c>
       <c r="F15" t="n">
-        <v>4.396</v>
+        <v>2.974</v>
       </c>
       <c r="G15" t="n">
-        <v>19803.225</v>
+        <v>57548.4</v>
       </c>
       <c r="H15" t="n">
-        <v>6.032</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>34.807</v>
+        <v>10.647</v>
       </c>
       <c r="J15" t="n">
-        <v>1.806</v>
+        <v>4.318</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Gasonline Vehicle (20%)</t>
+          <t>eVTOL</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.248</v>
+        <v>5.047</v>
       </c>
       <c r="C16" t="n">
-        <v>64.235</v>
+        <v>18.421</v>
       </c>
       <c r="D16" t="n">
-        <v>8.454000000000001</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>14.287</v>
+        <v>12.836</v>
       </c>
       <c r="F16" t="n">
-        <v>2.974</v>
+        <v>3.688</v>
       </c>
       <c r="G16" t="n">
-        <v>57548.4</v>
+        <v>22444.601</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>5.68</v>
       </c>
       <c r="I16" t="n">
-        <v>10.647</v>
+        <v>38.188</v>
       </c>
       <c r="J16" t="n">
-        <v>4.318</v>
+        <v>1.454</v>
       </c>
     </row>
     <row r="17">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.109</v>
+        <v>3.11</v>
       </c>
       <c r="C17" t="n">
         <v>179.595</v>
       </c>
       <c r="D17" t="n">
-        <v>4.576</v>
+        <v>4.578</v>
       </c>
       <c r="E17" t="n">
         <v>14.553</v>
@@ -3235,7 +3235,7 @@
         <v>179.595</v>
       </c>
       <c r="D18" t="n">
-        <v>4.576</v>
+        <v>4.578</v>
       </c>
       <c r="E18" t="n">
         <v>18.302</v>

--- a/src/results/TOC/optimized_results_TOC.xlsx
+++ b/src/results/TOC/optimized_results_TOC.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.895</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>9.874000000000001</v>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.051</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.002</v>
+        <v>0.832</v>
       </c>
       <c r="D5" t="n">
         <v>0.856</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.687</v>
+        <v>1.371</v>
       </c>
       <c r="D6" t="n">
         <v>1.395</v>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.006</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>2.025</v>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11.895</v>
+        <v>14.267</v>
       </c>
       <c r="D10" t="n">
         <v>9.874000000000001</v>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.536</v>
+        <v>0.543</v>
       </c>
       <c r="D11" t="n">
         <v>0.528</v>
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="D12" t="n">
         <v>0.051</v>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.867</v>
+        <v>11.327</v>
       </c>
       <c r="D13" t="n">
         <v>10.364</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1752.916</v>
+        <v>1298.44</v>
       </c>
       <c r="D14" t="n">
         <v>1531.77</v>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.956</v>
+        <v>0.975</v>
       </c>
       <c r="D15" t="n">
         <v>0.9350000000000001</v>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.066</v>
       </c>
       <c r="D16" t="n">
         <v>0.075</v>
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13.605</v>
+        <v>14.725</v>
       </c>
       <c r="D17" t="n">
         <v>12.479</v>
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1393.237</v>
+        <v>993.655</v>
       </c>
       <c r="D18" t="n">
         <v>1266.105</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>69.858</v>
+        <v>52.965</v>
       </c>
       <c r="D20" t="n">
         <v>70.524</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52.156</v>
+        <v>39.415</v>
       </c>
       <c r="D21" t="n">
         <v>52.859</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>51.648</v>
+        <v>39.032</v>
       </c>
       <c r="D22" t="n">
         <v>52.344</v>
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.259</v>
+        <v>5.486</v>
       </c>
       <c r="D23" t="n">
         <v>7.357</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4057.212</v>
+        <v>3050.027</v>
       </c>
       <c r="D25" t="n">
         <v>3486.582</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4057.212</v>
+        <v>3050.027</v>
       </c>
       <c r="D26" t="n">
         <v>3486.582</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>322427.265</v>
+        <v>202145.183</v>
       </c>
       <c r="D27" t="n">
         <v>285824.324</v>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>322427.265</v>
+        <v>202145.183</v>
       </c>
       <c r="D28" t="n">
         <v>285824.324</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1755.321</v>
+        <v>1300.222</v>
       </c>
       <c r="D29" t="n">
         <v>1533.872</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1755.321</v>
+        <v>1300.222</v>
       </c>
       <c r="D30" t="n">
         <v>1533.872</v>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>167436.031</v>
+        <v>97266.04399999999</v>
       </c>
       <c r="D31" t="n">
         <v>148752.248</v>
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>167436.031</v>
+        <v>97266.04399999999</v>
       </c>
       <c r="D32" t="n">
         <v>148752.248</v>
@@ -1009,7 +1009,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19141.451</v>
+        <v>14775.642</v>
       </c>
       <c r="D33" t="n">
         <v>15954.791</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2392.681</v>
+        <v>1846.955</v>
       </c>
       <c r="D34" t="n">
         <v>1994.349</v>
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>317567.349</v>
+        <v>265025.448</v>
       </c>
       <c r="D35" t="n">
         <v>292245.381</v>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39695.919</v>
+        <v>33128.181</v>
       </c>
       <c r="D36" t="n">
         <v>36530.673</v>
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>267.651</v>
+        <v>312.845</v>
       </c>
       <c r="D37" t="n">
         <v>326.257</v>
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.764</v>
+        <v>3.658</v>
       </c>
       <c r="D39" t="n">
         <v>2.728</v>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14.657</v>
+        <v>19.331</v>
       </c>
       <c r="D40" t="n">
         <v>14.518</v>
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18.421</v>
+        <v>23.989</v>
       </c>
       <c r="D41" t="n">
         <v>18.246</v>
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5292.789</v>
+        <v>4417.091</v>
       </c>
       <c r="D43" t="n">
         <v>4870.756</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>14855.325</v>
+        <v>12324</v>
       </c>
       <c r="D44" t="n">
         <v>12993.774</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40901.202</v>
+        <v>31338.246</v>
       </c>
       <c r="D45" t="n">
         <v>35994.088</v>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>61049.315</v>
+        <v>48079.337</v>
       </c>
       <c r="D46" t="n">
         <v>53858.618</v>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>55812.01</v>
+        <v>32422.015</v>
       </c>
       <c r="D47" t="n">
         <v>49584.083</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>116861.326</v>
+        <v>80501.352</v>
       </c>
       <c r="D48" t="n">
         <v>103442.701</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>182595.821</v>
+        <v>125783.363</v>
       </c>
       <c r="D49" t="n">
         <v>161629.221</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>65734.496</v>
+        <v>45282.011</v>
       </c>
       <c r="D50" t="n">
         <v>58186.519</v>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16.436</v>
+        <v>12.808</v>
       </c>
       <c r="D52" t="n">
         <v>13.092</v>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>64.03100000000001</v>
+        <v>48.238</v>
       </c>
       <c r="D53" t="n">
         <v>54.683</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>62.737</v>
+        <v>40.392</v>
       </c>
       <c r="D54" t="n">
         <v>44.632</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>117.888</v>
+        <v>91.41500000000001</v>
       </c>
       <c r="D55" t="n">
         <v>114.034</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>274.335</v>
+        <v>219.387</v>
       </c>
       <c r="D56" t="n">
         <v>254.147</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>147.925</v>
+        <v>115.269</v>
       </c>
       <c r="D57" t="n">
         <v>117.824</v>
@@ -1460,7 +1460,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>92.42</v>
+        <v>77.45399999999999</v>
       </c>
       <c r="D58" t="n">
         <v>80.85899999999999</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>93.929</v>
+        <v>110.269</v>
       </c>
       <c r="D59" t="n">
         <v>66.828</v>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>608.653</v>
+        <v>314.458</v>
       </c>
       <c r="D62" t="n">
         <v>404.073</v>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>949.765</v>
+        <v>798.923</v>
       </c>
       <c r="D63" t="n">
         <v>829.5069999999999</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1951.218</v>
+        <v>1506.182</v>
       </c>
       <c r="D64" t="n">
         <v>1626.38</v>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1951.218</v>
+        <v>1506.182</v>
       </c>
       <c r="D65" t="n">
         <v>1626.38</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.312</v>
+        <v>0.209</v>
       </c>
       <c r="D66" t="n">
         <v>0.248</v>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.487</v>
+        <v>0.53</v>
       </c>
       <c r="D67" t="n">
         <v>0.51</v>
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.772</v>
+        <v>1.473</v>
       </c>
       <c r="D69" t="n">
         <v>0.885</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1788.975</v>
+        <v>2231.571</v>
       </c>
       <c r="D70" t="n">
         <v>2289.977</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>24.896</v>
+        <v>29.636</v>
       </c>
       <c r="D71" t="n">
         <v>27.264</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2719.817</v>
+        <v>3417.856</v>
       </c>
       <c r="D72" t="n">
         <v>3452.523</v>
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>48.166</v>
+        <v>53.283</v>
       </c>
       <c r="D73" t="n">
         <v>50.103</v>
@@ -1756,7 +1756,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>736.716</v>
+        <v>980.109</v>
       </c>
       <c r="D74" t="n">
         <v>983.6319999999999</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>72.09999999999999</v>
+        <v>73.55500000000001</v>
       </c>
       <c r="D75" t="n">
         <v>74.583</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.739</v>
+        <v>2.107</v>
       </c>
       <c r="D77" t="n">
         <v>1.808</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.766</v>
+        <v>1.607</v>
       </c>
       <c r="D78" t="n">
         <v>1.768</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.917</v>
+        <v>0.773</v>
       </c>
       <c r="D79" t="n">
         <v>0.92</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.089</v>
+        <v>0.956</v>
       </c>
       <c r="D80" t="n">
         <v>1.096</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.334</v>
+        <v>0.382</v>
       </c>
       <c r="D81" t="n">
         <v>0.333</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1930.165</v>
+        <v>4984.565</v>
       </c>
       <c r="D82" t="n">
         <v>1896.176</v>
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2.275</v>
+        <v>0.534</v>
       </c>
       <c r="D83" t="n">
         <v>2.341</v>
@@ -1949,7 +1949,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10.001</v>
+        <v>22.934</v>
       </c>
       <c r="D85" t="n">
         <v>9.872</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>28.422</v>
+        <v>46.924</v>
       </c>
       <c r="D86" t="n">
         <v>28.118</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.543</v>
+        <v>1.956</v>
       </c>
       <c r="D87" t="n">
         <v>1.541</v>
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>16.888</v>
+        <v>10.229</v>
       </c>
       <c r="D88" t="n">
         <v>17.071</v>
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.185</v>
+        <v>4.09</v>
       </c>
       <c r="D89" t="n">
         <v>5.191</v>
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4390.919</v>
+        <v>2659.632</v>
       </c>
       <c r="D90" t="n">
         <v>4438.501</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1348.098</v>
+        <v>1063.384</v>
       </c>
       <c r="D91" t="n">
         <v>1349.751</v>
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>22733.18</v>
+        <v>15660.029</v>
       </c>
       <c r="D93" t="n">
         <v>20122.838</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>51715.546</v>
+        <v>8355.778</v>
       </c>
       <c r="D94" t="n">
         <v>47102.821</v>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>11.778</v>
+        <v>3.142</v>
       </c>
       <c r="D95" t="n">
         <v>10.612</v>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>23.135</v>
+        <v>18.22</v>
       </c>
       <c r="D96" t="n">
         <v>20.41</v>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>34.913</v>
+        <v>21.362</v>
       </c>
       <c r="D97" t="n">
         <v>31.023</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>153300.553</v>
+        <v>56814.665</v>
       </c>
       <c r="D98" t="n">
         <v>137693.781</v>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>66.265</v>
+        <v>85.29300000000001</v>
       </c>
       <c r="D99" t="n">
         <v>65.792</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>33.735</v>
+        <v>14.707</v>
       </c>
       <c r="D100" t="n">
         <v>34.208</v>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5.902</v>
+        <v>4.648</v>
       </c>
       <c r="D102" t="n">
         <v>5.206</v>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>19.357</v>
+        <v>16.64</v>
       </c>
       <c r="D103" t="n">
         <v>17.402</v>
@@ -2294,7 +2294,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.729</v>
+        <v>17.714</v>
       </c>
       <c r="D104" t="n">
         <v>10.614</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10.132</v>
+        <v>13.194</v>
       </c>
       <c r="D105" t="n">
         <v>10.035</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>20998.519</v>
+        <v>14465.087</v>
       </c>
       <c r="D106" t="n">
         <v>18587.36</v>
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>10.879</v>
+        <v>2.902</v>
       </c>
       <c r="D107" t="n">
         <v>9.803000000000001</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>21.011</v>
+        <v>16.096</v>
       </c>
       <c r="D108" t="n">
         <v>19.838</v>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>56.999</v>
+        <v>55.098</v>
       </c>
       <c r="D109" t="n">
         <v>53.061</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>28.153</v>
+        <v>37.654</v>
       </c>
       <c r="D110" t="n">
         <v>24.554</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>85.152</v>
+        <v>92.752</v>
       </c>
       <c r="D111" t="n">
         <v>77.61499999999999</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>18.718</v>
+        <v>20.389</v>
       </c>
       <c r="D112" t="n">
         <v>17.061</v>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>103.87</v>
+        <v>113.141</v>
       </c>
       <c r="D113" t="n">
         <v>94.676</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.371</v>
+        <v>0.404</v>
       </c>
       <c r="D114" t="n">
         <v>0.338</v>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.41</v>
+        <v>1.179</v>
       </c>
       <c r="D115" t="n">
         <v>1.297</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>273.122</v>
+        <v>263.851</v>
       </c>
       <c r="D120" t="n">
         <v>282.316</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1199255.011</v>
+        <v>701746.796</v>
       </c>
       <c r="D121" t="n">
         <v>1253059.328</v>
@@ -2685,13 +2685,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7</v>
+        <v>7.753</v>
       </c>
       <c r="C2" t="n">
         <v>64.235</v>
       </c>
       <c r="D2" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1.183</v>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.519</v>
+        <v>7.572</v>
       </c>
       <c r="C3" t="n">
         <v>64.235</v>
       </c>
       <c r="D3" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>2.366</v>
@@ -2753,13 +2753,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.431</v>
+        <v>7.487</v>
       </c>
       <c r="C4" t="n">
         <v>50.909</v>
       </c>
       <c r="D4" t="n">
-        <v>8.907</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.588</v>
@@ -2787,13 +2787,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.426</v>
+        <v>7.478</v>
       </c>
       <c r="C5" t="n">
         <v>64.235</v>
       </c>
       <c r="D5" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>2.821</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.032</v>
+        <v>7.075</v>
       </c>
       <c r="C6" t="n">
         <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>7.087</v>
+        <v>7.217</v>
       </c>
       <c r="E6" t="n">
         <v>1.456</v>
@@ -2851,69 +2851,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Electric Vehicle (26%)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.999</v>
+        <v>7.012</v>
       </c>
       <c r="C7" t="n">
-        <v>285.957</v>
+        <v>64.235</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>7.762</v>
       </c>
       <c r="G7" t="n">
-        <v>-9955.456</v>
+        <v>12089.35</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>7.061</v>
       </c>
       <c r="I7" t="n">
-        <v>-43.994</v>
+        <v>7.371</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>4.659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Electric Vehicle (26%)</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.959</v>
+        <v>6.999</v>
       </c>
       <c r="C8" t="n">
-        <v>64.235</v>
+        <v>285.957</v>
       </c>
       <c r="D8" t="n">
-        <v>8.459</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7.762</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>12089.35</v>
+        <v>-9955.456</v>
       </c>
       <c r="H8" t="n">
-        <v>7.061</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>7.371</v>
+        <v>-43.994</v>
       </c>
       <c r="J8" t="n">
-        <v>4.659</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2923,13 +2923,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.774</v>
+        <v>6.83</v>
       </c>
       <c r="C9" t="n">
         <v>50.909</v>
       </c>
       <c r="D9" t="n">
-        <v>8.907</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>1.008</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.696</v>
+        <v>6.739</v>
       </c>
       <c r="C10" t="n">
         <v>105</v>
       </c>
       <c r="D10" t="n">
-        <v>7.087</v>
+        <v>7.217</v>
       </c>
       <c r="E10" t="n">
         <v>2.464</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.66</v>
+        <v>6.713</v>
       </c>
       <c r="C11" t="n">
         <v>64.235</v>
       </c>
       <c r="D11" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>5.915</v>
@@ -3025,13 +3025,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.282</v>
+        <v>6.335</v>
       </c>
       <c r="C12" t="n">
         <v>64.235</v>
       </c>
       <c r="D12" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>9.009</v>
@@ -3059,13 +3059,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.887</v>
+        <v>5.94</v>
       </c>
       <c r="C13" t="n">
         <v>64.235</v>
       </c>
       <c r="D13" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>10.92</v>
@@ -3093,13 +3093,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.79</v>
+        <v>5.842</v>
       </c>
       <c r="C14" t="n">
         <v>64.235</v>
       </c>
       <c r="D14" t="n">
-        <v>8.459</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>11.648</v>
@@ -3123,69 +3123,69 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gasonline Vehicle (20%)</t>
+          <t>eVTOL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.25</v>
+        <v>5.745</v>
       </c>
       <c r="C15" t="n">
-        <v>64.235</v>
+        <v>23.989</v>
       </c>
       <c r="D15" t="n">
-        <v>8.459</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>14.287</v>
+        <v>7.854</v>
       </c>
       <c r="F15" t="n">
-        <v>2.974</v>
+        <v>6.138</v>
       </c>
       <c r="G15" t="n">
-        <v>57548.4</v>
+        <v>17676.227</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>6.316</v>
       </c>
       <c r="I15" t="n">
-        <v>10.647</v>
+        <v>41.596</v>
       </c>
       <c r="J15" t="n">
-        <v>4.318</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>eVTOL</t>
+          <t>Gasonline Vehicle (20%)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.047</v>
+        <v>5.303</v>
       </c>
       <c r="C16" t="n">
-        <v>18.421</v>
+        <v>64.235</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>12.836</v>
+        <v>14.287</v>
       </c>
       <c r="F16" t="n">
-        <v>3.688</v>
+        <v>2.974</v>
       </c>
       <c r="G16" t="n">
-        <v>22444.601</v>
+        <v>57548.4</v>
       </c>
       <c r="H16" t="n">
-        <v>5.68</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>38.188</v>
+        <v>10.647</v>
       </c>
       <c r="J16" t="n">
-        <v>1.454</v>
+        <v>4.318</v>
       </c>
     </row>
     <row r="17">
@@ -3195,13 +3195,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.11</v>
+        <v>3.135</v>
       </c>
       <c r="C17" t="n">
         <v>179.595</v>
       </c>
       <c r="D17" t="n">
-        <v>4.578</v>
+        <v>4.654</v>
       </c>
       <c r="E17" t="n">
         <v>14.553</v>
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.192</v>
+        <v>2.218</v>
       </c>
       <c r="C18" t="n">
         <v>179.595</v>
       </c>
       <c r="D18" t="n">
-        <v>4.578</v>
+        <v>4.654</v>
       </c>
       <c r="E18" t="n">
         <v>18.302</v>

--- a/src/results/TOC/optimized_results_TOC.xlsx
+++ b/src/results/TOC/optimized_results_TOC.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>9.874000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>9.874000000000001</v>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.051</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.832</v>
+        <v>0.856</v>
       </c>
       <c r="D5" t="n">
         <v>0.856</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.371</v>
+        <v>1.395</v>
       </c>
       <c r="D6" t="n">
         <v>1.395</v>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2.025</v>
       </c>
       <c r="D8" t="n">
         <v>2.025</v>
@@ -588,11 +588,9 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14.267</v>
-      </c>
-      <c r="D10" t="n">
         <v>9.874000000000001</v>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -607,11 +605,9 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.543</v>
-      </c>
-      <c r="D11" t="n">
         <v>0.528</v>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -626,11 +622,9 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D12" t="n">
         <v>0.051</v>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -645,11 +639,9 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11.327</v>
-      </c>
-      <c r="D13" t="n">
         <v>10.364</v>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -664,11 +656,9 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1298.44</v>
-      </c>
-      <c r="D14" t="n">
         <v>1531.77</v>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>N</t>
@@ -683,11 +673,9 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="D15" t="n">
         <v>0.9350000000000001</v>
       </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -702,11 +690,9 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="D16" t="n">
         <v>0.075</v>
       </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -721,11 +707,9 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.725</v>
-      </c>
-      <c r="D17" t="n">
         <v>12.479</v>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -740,11 +724,9 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>993.655</v>
-      </c>
-      <c r="D18" t="n">
         <v>1266.105</v>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>N</t>
@@ -770,11 +752,9 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>52.965</v>
-      </c>
-      <c r="D20" t="n">
         <v>70.524</v>
       </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>m/s</t>
@@ -789,11 +769,9 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39.415</v>
-      </c>
-      <c r="D21" t="n">
         <v>52.859</v>
       </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>m/s</t>
@@ -808,11 +786,9 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>39.032</v>
-      </c>
-      <c r="D22" t="n">
         <v>52.344</v>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>m/s</t>
@@ -827,11 +803,9 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.486</v>
-      </c>
-      <c r="D23" t="n">
         <v>7.357</v>
       </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>m/s</t>
@@ -857,11 +831,9 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3050.027</v>
-      </c>
-      <c r="D25" t="n">
         <v>3486.582</v>
       </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>N</t>
@@ -876,11 +848,9 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3050.027</v>
-      </c>
-      <c r="D26" t="n">
         <v>3486.582</v>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>N</t>
@@ -895,11 +865,9 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>202145.183</v>
-      </c>
-      <c r="D27" t="n">
-        <v>285824.324</v>
-      </c>
+        <v>285824.325</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>W</t>
@@ -914,11 +882,9 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>202145.183</v>
-      </c>
-      <c r="D28" t="n">
-        <v>285824.324</v>
-      </c>
+        <v>285824.325</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>W</t>
@@ -933,11 +899,9 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1300.222</v>
-      </c>
-      <c r="D29" t="n">
         <v>1533.872</v>
       </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>N</t>
@@ -952,11 +916,9 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1300.222</v>
-      </c>
-      <c r="D30" t="n">
         <v>1533.872</v>
       </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>N</t>
@@ -971,11 +933,9 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>97266.04399999999</v>
-      </c>
-      <c r="D31" t="n">
         <v>148752.248</v>
       </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
           <t>W</t>
@@ -990,11 +950,9 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>97266.04399999999</v>
-      </c>
-      <c r="D32" t="n">
         <v>148752.248</v>
       </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
           <t>W</t>
@@ -1009,11 +967,9 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14775.642</v>
-      </c>
-      <c r="D33" t="n">
         <v>15954.791</v>
       </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>N</t>
@@ -1028,11 +984,9 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1846.955</v>
-      </c>
-      <c r="D34" t="n">
         <v>1994.349</v>
       </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>N</t>
@@ -1047,11 +1001,9 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>265025.448</v>
-      </c>
-      <c r="D35" t="n">
         <v>292245.381</v>
       </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>W</t>
@@ -1066,11 +1018,9 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>33128.181</v>
-      </c>
-      <c r="D36" t="n">
         <v>36530.673</v>
       </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>W</t>
@@ -1085,11 +1035,9 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>312.845</v>
-      </c>
-      <c r="D37" t="n">
         <v>326.257</v>
       </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>N/m²</t>
@@ -1115,11 +1063,9 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.658</v>
-      </c>
-      <c r="D39" t="n">
         <v>2.728</v>
       </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>min</t>
@@ -1134,11 +1080,9 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>19.331</v>
-      </c>
-      <c r="D40" t="n">
         <v>14.518</v>
       </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
           <t>min</t>
@@ -1153,11 +1097,9 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>23.989</v>
-      </c>
-      <c r="D41" t="n">
         <v>18.246</v>
       </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>min</t>
@@ -1183,11 +1125,9 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4417.091</v>
-      </c>
-      <c r="D43" t="n">
         <v>4870.756</v>
       </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1202,11 +1142,9 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12324</v>
-      </c>
-      <c r="D44" t="n">
         <v>12993.774</v>
       </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1221,11 +1159,9 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>31338.246</v>
-      </c>
-      <c r="D45" t="n">
         <v>35994.088</v>
       </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1240,11 +1176,9 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>48079.337</v>
-      </c>
-      <c r="D46" t="n">
         <v>53858.618</v>
       </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1259,11 +1193,9 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>32422.015</v>
-      </c>
-      <c r="D47" t="n">
         <v>49584.083</v>
       </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1278,11 +1210,9 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80501.352</v>
-      </c>
-      <c r="D48" t="n">
         <v>103442.701</v>
       </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1297,11 +1227,9 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>125783.363</v>
-      </c>
-      <c r="D49" t="n">
         <v>161629.221</v>
       </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1316,11 +1244,9 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>45282.011</v>
-      </c>
-      <c r="D50" t="n">
         <v>58186.519</v>
       </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>Wh</t>
@@ -1346,11 +1272,9 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>12.808</v>
-      </c>
-      <c r="D52" t="n">
         <v>13.092</v>
       </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1365,11 +1289,9 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>48.238</v>
-      </c>
-      <c r="D53" t="n">
         <v>54.683</v>
       </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1384,11 +1306,9 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40.392</v>
-      </c>
-      <c r="D54" t="n">
         <v>44.632</v>
       </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1403,11 +1323,9 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>91.41500000000001</v>
-      </c>
-      <c r="D55" t="n">
         <v>114.034</v>
       </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1422,11 +1340,9 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>219.387</v>
-      </c>
-      <c r="D56" t="n">
         <v>254.147</v>
       </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1441,11 +1357,9 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>115.269</v>
-      </c>
-      <c r="D57" t="n">
         <v>117.824</v>
       </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1460,11 +1374,9 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>77.45399999999999</v>
-      </c>
-      <c r="D58" t="n">
         <v>80.85899999999999</v>
       </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1479,11 +1391,9 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>110.269</v>
-      </c>
-      <c r="D59" t="n">
         <v>66.828</v>
       </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1500,9 +1410,7 @@
       <c r="C60" t="n">
         <v>392.8</v>
       </c>
-      <c r="D60" t="n">
-        <v>392.8</v>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1519,9 +1427,7 @@
       <c r="C61" t="n">
         <v>96.5</v>
       </c>
-      <c r="D61" t="n">
-        <v>96.5</v>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1536,11 +1442,9 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>314.458</v>
-      </c>
-      <c r="D62" t="n">
         <v>404.073</v>
       </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1555,11 +1459,9 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>798.923</v>
-      </c>
-      <c r="D63" t="n">
         <v>829.5069999999999</v>
       </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1574,11 +1476,9 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1506.182</v>
-      </c>
-      <c r="D64" t="n">
         <v>1626.38</v>
       </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1593,11 +1493,9 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1506.182</v>
-      </c>
-      <c r="D65" t="n">
         <v>1626.38</v>
       </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1612,11 +1510,9 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="D66" t="n">
         <v>0.248</v>
       </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -1631,11 +1527,9 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D67" t="n">
         <v>0.51</v>
       </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -1661,11 +1555,9 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1.473</v>
-      </c>
-      <c r="D69" t="n">
         <v>0.885</v>
       </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -1680,11 +1572,9 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2231.571</v>
-      </c>
-      <c r="D70" t="n">
         <v>2289.977</v>
       </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>RPM</t>
@@ -1699,11 +1589,9 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>29.636</v>
-      </c>
-      <c r="D71" t="n">
         <v>27.264</v>
       </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>dB</t>
@@ -1718,11 +1606,9 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3417.856</v>
-      </c>
-      <c r="D72" t="n">
         <v>3452.523</v>
       </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>RPM</t>
@@ -1737,11 +1623,9 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>53.283</v>
-      </c>
-      <c r="D73" t="n">
         <v>50.103</v>
       </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>dB</t>
@@ -1756,11 +1640,9 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>980.109</v>
-      </c>
-      <c r="D74" t="n">
         <v>983.6319999999999</v>
       </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>RPM</t>
@@ -1775,11 +1657,9 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>73.55500000000001</v>
-      </c>
-      <c r="D75" t="n">
         <v>74.583</v>
       </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>dB</t>
@@ -1805,11 +1685,9 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2.107</v>
-      </c>
-      <c r="D77" t="n">
         <v>1.808</v>
       </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>1/h</t>
@@ -1824,11 +1702,9 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.607</v>
-      </c>
-      <c r="D78" t="n">
         <v>1.768</v>
       </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>1/h</t>
@@ -1843,11 +1719,9 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="D79" t="n">
         <v>0.92</v>
       </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>1/h</t>
@@ -1862,11 +1736,9 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.956</v>
-      </c>
-      <c r="D80" t="n">
         <v>1.096</v>
       </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>1/h</t>
@@ -1881,11 +1753,9 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="D81" t="n">
         <v>0.333</v>
       </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -1900,11 +1770,9 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4984.565</v>
-      </c>
-      <c r="D82" t="n">
         <v>1896.176</v>
       </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -1919,11 +1787,9 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="D83" t="n">
         <v>2.341</v>
       </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -1949,11 +1815,9 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>22.934</v>
-      </c>
-      <c r="D85" t="n">
         <v>9.872</v>
       </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>min</t>
@@ -1968,11 +1832,9 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>46.924</v>
-      </c>
-      <c r="D86" t="n">
         <v>28.118</v>
       </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>min</t>
@@ -1987,11 +1849,9 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.956</v>
-      </c>
-      <c r="D87" t="n">
         <v>1.541</v>
       </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -2006,11 +1866,9 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10.229</v>
-      </c>
-      <c r="D88" t="n">
         <v>17.071</v>
       </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>flights</t>
@@ -2025,11 +1883,9 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="D89" t="n">
         <v>5.191</v>
       </c>
+      <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
           <t>hours</t>
@@ -2044,11 +1900,9 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2659.632</v>
-      </c>
-      <c r="D90" t="n">
         <v>4438.501</v>
       </c>
+      <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
           <t>flights</t>
@@ -2063,11 +1917,9 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1063.384</v>
-      </c>
-      <c r="D91" t="n">
         <v>1349.751</v>
       </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
           <t>hours</t>
@@ -2093,11 +1945,9 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>15660.029</v>
-      </c>
-      <c r="D93" t="n">
         <v>20122.838</v>
       </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>kg CO2e</t>
@@ -2112,11 +1962,9 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8355.778</v>
-      </c>
-      <c r="D94" t="n">
         <v>47102.821</v>
       </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>kg CO2e</t>
@@ -2131,11 +1979,9 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3.142</v>
-      </c>
-      <c r="D95" t="n">
         <v>10.612</v>
       </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>kg CO2e</t>
@@ -2150,11 +1996,9 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="D96" t="n">
         <v>20.41</v>
       </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>kg CO2e</t>
@@ -2169,11 +2013,9 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>21.362</v>
-      </c>
-      <c r="D97" t="n">
         <v>31.023</v>
       </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>kg CO2e</t>
@@ -2188,11 +2030,9 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>56814.665</v>
-      </c>
-      <c r="D98" t="n">
         <v>137693.781</v>
       </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>kg CO2e</t>
@@ -2207,11 +2047,9 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>85.29300000000001</v>
-      </c>
-      <c r="D99" t="n">
         <v>65.792</v>
       </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
           <t>%</t>
@@ -2226,11 +2064,9 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>14.707</v>
-      </c>
-      <c r="D100" t="n">
         <v>34.208</v>
       </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>%</t>
@@ -2256,11 +2092,9 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>4.648</v>
-      </c>
-      <c r="D102" t="n">
         <v>5.206</v>
       </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>€</t>
@@ -2275,11 +2109,9 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="D103" t="n">
         <v>17.402</v>
       </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>€</t>
@@ -2294,11 +2126,9 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>17.714</v>
-      </c>
-      <c r="D104" t="n">
         <v>10.614</v>
       </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>€</t>
@@ -2313,11 +2143,9 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>13.194</v>
-      </c>
-      <c r="D105" t="n">
         <v>10.035</v>
       </c>
+      <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
           <t>€</t>
@@ -2332,11 +2160,9 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>14465.087</v>
-      </c>
-      <c r="D106" t="n">
         <v>18587.36</v>
       </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>€</t>
@@ -2351,11 +2177,9 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2.902</v>
-      </c>
-      <c r="D107" t="n">
         <v>9.803000000000001</v>
       </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>€</t>
@@ -2370,11 +2194,9 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>16.096</v>
-      </c>
-      <c r="D108" t="n">
         <v>19.838</v>
       </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>€</t>
@@ -2389,11 +2211,9 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>55.098</v>
-      </c>
-      <c r="D109" t="n">
         <v>53.061</v>
       </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>€</t>
@@ -2408,11 +2228,9 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>37.654</v>
-      </c>
-      <c r="D110" t="n">
         <v>24.554</v>
       </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
           <t>€</t>
@@ -2427,11 +2245,9 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>92.752</v>
-      </c>
-      <c r="D111" t="n">
         <v>77.61499999999999</v>
       </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>€</t>
@@ -2446,11 +2262,9 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>20.389</v>
-      </c>
-      <c r="D112" t="n">
         <v>17.061</v>
       </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>€</t>
@@ -2465,11 +2279,9 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>113.141</v>
-      </c>
-      <c r="D113" t="n">
         <v>94.676</v>
       </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
           <t>€</t>
@@ -2484,11 +2296,9 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.404</v>
-      </c>
-      <c r="D114" t="n">
         <v>0.338</v>
       </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>€/km</t>
@@ -2503,11 +2313,9 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1.179</v>
-      </c>
-      <c r="D115" t="n">
         <v>1.297</v>
       </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>€/min</t>
@@ -2535,9 +2343,7 @@
       <c r="C117" t="n">
         <v>138.6</v>
       </c>
-      <c r="D117" t="n">
-        <v>138.6</v>
-      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>€</t>
@@ -2554,9 +2360,7 @@
       <c r="C118" t="n">
         <v>376.992</v>
       </c>
-      <c r="D118" t="n">
-        <v>376.992</v>
-      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>€</t>
@@ -2582,11 +2386,9 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>263.851</v>
-      </c>
-      <c r="D120" t="n">
         <v>282.316</v>
       </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>€</t>
@@ -2601,11 +2403,9 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>701746.796</v>
-      </c>
-      <c r="D121" t="n">
         <v>1253059.328</v>
       </c>
+      <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
           <t>€</t>
@@ -2685,13 +2485,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.753</v>
+        <v>7.699</v>
       </c>
       <c r="C2" t="n">
         <v>64.235</v>
       </c>
       <c r="D2" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1.183</v>
@@ -2719,13 +2519,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.572</v>
+        <v>7.518</v>
       </c>
       <c r="C3" t="n">
         <v>64.235</v>
       </c>
       <c r="D3" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>2.366</v>
@@ -2753,13 +2553,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.487</v>
+        <v>7.43</v>
       </c>
       <c r="C4" t="n">
         <v>50.909</v>
       </c>
       <c r="D4" t="n">
-        <v>9.074999999999999</v>
+        <v>8.901999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.588</v>
@@ -2787,13 +2587,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.478</v>
+        <v>7.424</v>
       </c>
       <c r="C5" t="n">
         <v>64.235</v>
       </c>
       <c r="D5" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>2.821</v>
@@ -2821,13 +2621,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.075</v>
+        <v>7.031</v>
       </c>
       <c r="C6" t="n">
         <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>7.217</v>
+        <v>7.083</v>
       </c>
       <c r="E6" t="n">
         <v>1.456</v>
@@ -2851,69 +2651,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Electric Vehicle (26%)</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.012</v>
+        <v>6.999</v>
       </c>
       <c r="C7" t="n">
-        <v>64.235</v>
+        <v>285.957</v>
       </c>
       <c r="D7" t="n">
-        <v>8.617000000000001</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>7.762</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>12089.35</v>
+        <v>-9955.456</v>
       </c>
       <c r="H7" t="n">
-        <v>7.061</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>7.371</v>
+        <v>-43.994</v>
       </c>
       <c r="J7" t="n">
-        <v>4.659</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Electric Vehicle (26%)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.999</v>
+        <v>6.958</v>
       </c>
       <c r="C8" t="n">
-        <v>285.957</v>
+        <v>64.235</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>7.762</v>
       </c>
       <c r="G8" t="n">
-        <v>-9955.456</v>
+        <v>12089.35</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>7.061</v>
       </c>
       <c r="I8" t="n">
-        <v>-43.994</v>
+        <v>7.371</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>4.659</v>
       </c>
     </row>
     <row r="9">
@@ -2923,13 +2723,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.83</v>
+        <v>6.773</v>
       </c>
       <c r="C9" t="n">
         <v>50.909</v>
       </c>
       <c r="D9" t="n">
-        <v>9.074999999999999</v>
+        <v>8.901999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>1.008</v>
@@ -2957,13 +2757,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.739</v>
+        <v>6.695</v>
       </c>
       <c r="C10" t="n">
         <v>105</v>
       </c>
       <c r="D10" t="n">
-        <v>7.217</v>
+        <v>7.083</v>
       </c>
       <c r="E10" t="n">
         <v>2.464</v>
@@ -2991,13 +2791,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.713</v>
+        <v>6.658</v>
       </c>
       <c r="C11" t="n">
         <v>64.235</v>
       </c>
       <c r="D11" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>5.915</v>
@@ -3025,13 +2825,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.335</v>
+        <v>6.28</v>
       </c>
       <c r="C12" t="n">
         <v>64.235</v>
       </c>
       <c r="D12" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>9.009</v>
@@ -3059,13 +2859,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.94</v>
+        <v>5.885</v>
       </c>
       <c r="C13" t="n">
         <v>64.235</v>
       </c>
       <c r="D13" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>10.92</v>
@@ -3093,13 +2893,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.842</v>
+        <v>5.788</v>
       </c>
       <c r="C14" t="n">
         <v>64.235</v>
       </c>
       <c r="D14" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>11.648</v>
@@ -3127,31 +2927,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.745</v>
+        <v>5.398</v>
       </c>
       <c r="C15" t="n">
-        <v>23.989</v>
+        <v>18.246</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>7.854</v>
+        <v>11.405</v>
       </c>
       <c r="F15" t="n">
-        <v>6.138</v>
+        <v>4.391</v>
       </c>
       <c r="G15" t="n">
-        <v>17676.227</v>
+        <v>19800.963</v>
       </c>
       <c r="H15" t="n">
-        <v>6.316</v>
+        <v>6.033</v>
       </c>
       <c r="I15" t="n">
-        <v>41.596</v>
+        <v>34.807</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.806</v>
       </c>
     </row>
     <row r="16">
@@ -3161,13 +2961,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.303</v>
+        <v>5.248</v>
       </c>
       <c r="C16" t="n">
         <v>64.235</v>
       </c>
       <c r="D16" t="n">
-        <v>8.617000000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>14.287</v>
@@ -3195,13 +2995,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.135</v>
+        <v>3.109</v>
       </c>
       <c r="C17" t="n">
         <v>179.595</v>
       </c>
       <c r="D17" t="n">
-        <v>4.654</v>
+        <v>4.576</v>
       </c>
       <c r="E17" t="n">
         <v>14.553</v>
@@ -3229,13 +3029,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.218</v>
+        <v>2.192</v>
       </c>
       <c r="C18" t="n">
         <v>179.595</v>
       </c>
       <c r="D18" t="n">
-        <v>4.654</v>
+        <v>4.576</v>
       </c>
       <c r="E18" t="n">
         <v>18.302</v>

--- a/src/results/TOC/optimized_results_TOC.xlsx
+++ b/src/results/TOC/optimized_results_TOC.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.874000000000001</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>9.874000000000001</v>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>1.051</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.856</v>
+        <v>0.832</v>
       </c>
       <c r="D5" t="n">
         <v>0.856</v>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.395</v>
+        <v>1.371</v>
       </c>
       <c r="D6" t="n">
         <v>1.395</v>
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.025</v>
+        <v>2.554</v>
       </c>
       <c r="D8" t="n">
         <v>2.025</v>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9.874000000000001</v>
+        <v>14.267</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.528</v>
+        <v>0.543</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.051</v>
+        <v>0.048</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.364</v>
+        <v>11.327</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1531.77</v>
+        <v>1298.44</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.975</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.075</v>
+        <v>0.066</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.479</v>
+        <v>14.725</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1266.105</v>
+        <v>993.655</v>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>70.524</v>
+        <v>52.965</v>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>52.859</v>
+        <v>39.415</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52.344</v>
+        <v>39.032</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.357</v>
+        <v>5.486</v>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3486.582</v>
+        <v>3050.026</v>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3486.582</v>
+        <v>3050.026</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>285824.325</v>
+        <v>202145.319</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>285824.325</v>
+        <v>202145.319</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1533.872</v>
+        <v>1300.222</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1533.872</v>
+        <v>1300.222</v>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>148752.248</v>
+        <v>97266.087</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>148752.248</v>
+        <v>97266.087</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>15954.791</v>
+        <v>14775.642</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1994.349</v>
+        <v>1846.955</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>292245.381</v>
+        <v>265025.467</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36530.673</v>
+        <v>33128.183</v>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>326.257</v>
+        <v>312.845</v>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.728</v>
+        <v>3.658</v>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>14.518</v>
+        <v>19.331</v>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>18.246</v>
+        <v>23.989</v>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4870.756</v>
+        <v>4417.091</v>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>12993.774</v>
+        <v>12324.001</v>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35994.088</v>
+        <v>31338.239</v>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>53858.618</v>
+        <v>48079.331</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49584.083</v>
+        <v>32422.029</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>103442.701</v>
+        <v>80501.36</v>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>161629.221</v>
+        <v>125783.375</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>58186.519</v>
+        <v>45282.015</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>13.092</v>
+        <v>12.808</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.683</v>
+        <v>48.238</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>44.632</v>
+        <v>40.392</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>114.034</v>
+        <v>91.41500000000001</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>254.147</v>
+        <v>219.387</v>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>117.824</v>
+        <v>115.269</v>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>80.85899999999999</v>
+        <v>77.45399999999999</v>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>66.828</v>
+        <v>110.269</v>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>404.073</v>
+        <v>314.458</v>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>829.5069999999999</v>
+        <v>798.923</v>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
@@ -1472,11 +1472,11 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MTOM from model</t>
+          <t>MTOM</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1626.38</v>
+        <v>1506.182</v>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
@@ -1489,16 +1489,16 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MTOM iterated</t>
+          <t>Battery mass fraction</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1626.38</v>
+        <v>0.209</v>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1506,11 +1506,11 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Battery mass fraction</t>
+          <t>Empty mass fraction</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.248</v>
+        <v>0.53</v>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
@@ -1520,47 +1520,47 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Empty mass fraction</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0.51</v>
-      </c>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NOISE MODEL</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Thrust coefficient horizontal</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>NOISE MODEL</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Thrust coefficient horizontal</t>
+          <t>RPM in cruise</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.885</v>
+        <v>2231.577</v>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RPM</t>
         </is>
       </c>
     </row>
@@ -1568,16 +1568,16 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RPM in cruise</t>
+          <t>SPL in cruise</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2289.977</v>
+        <v>29.636</v>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>dB</t>
         </is>
       </c>
     </row>
@@ -1585,16 +1585,16 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPL in cruise</t>
+          <t>RPM in climb</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>27.264</v>
+        <v>3417.865</v>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>RPM</t>
         </is>
       </c>
     </row>
@@ -1602,16 +1602,16 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RPM in climb</t>
+          <t>SPL in climb</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3452.523</v>
+        <v>53.283</v>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>dB</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SPL in climb</t>
+          <t>RPM in hover</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50.103</v>
+        <v>980.109</v>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>dB</t>
+          <t>RPM</t>
         </is>
       </c>
     </row>
@@ -1636,56 +1636,56 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RPM in hover</t>
+          <t>SPL in hover</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>983.6319999999999</v>
+        <v>73.55500000000001</v>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>dB</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>SPL in hover</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>74.583</v>
-      </c>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BATTERY LIFE MODEL</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>dB</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BATTERY LIFE MODEL</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C-rate in hover</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2.107</v>
+      </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1/h</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>C-rate in hover</t>
+          <t>C-rate in climb</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1.808</v>
+        <v>1.607</v>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
@@ -1698,11 +1698,11 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>C-rate in climb</t>
+          <t>C-rate in cruise</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1.768</v>
+        <v>0.773</v>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
@@ -1715,11 +1715,11 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>C-rate in cruise</t>
+          <t>Time avg. c-rate per trip</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.92</v>
+        <v>0.956</v>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
@@ -1732,16 +1732,16 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Time avg. c-rate per trip</t>
+          <t>Depth of discharge (DoD)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1.096</v>
+        <v>0.382</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1/h</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Depth of discharge (DoD)</t>
+          <t>Battery cycle life</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.333</v>
+        <v>1618.193</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
@@ -1766,11 +1766,11 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Battery cycle life</t>
+          <t>Number of annual battery replacements</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1896.176</v>
+        <v>2.339</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
@@ -1780,42 +1780,42 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Number of annual battery replacements</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>2.341</v>
-      </c>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OPERATIONS MODEL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>OPERATIONS MODEL</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Turnaround time</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>8.981</v>
+      </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Turnaround time</t>
+          <t>Full leg time (flight + turnaround)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9.872</v>
+        <v>32.97</v>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
@@ -1828,16 +1828,16 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Full leg time (flight + turnaround)</t>
+          <t>Time Efficiency Ratio</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>28.118</v>
+        <v>1.374</v>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1845,16 +1845,16 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Time Efficiency Ratio</t>
+          <t>Daily flight cycles</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1.541</v>
+        <v>14.559</v>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>flights</t>
         </is>
       </c>
     </row>
@@ -1862,16 +1862,16 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Daily flight cycles</t>
+          <t>Daily flight hours</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>17.071</v>
+        <v>5.821</v>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Daily flight hours</t>
+          <t>Annual flight cycles</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5.191</v>
+        <v>3785.217</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>flights</t>
         </is>
       </c>
     </row>
@@ -1896,56 +1896,56 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Annual flight cycles</t>
+          <t>Annual flight hours</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4438.501</v>
+        <v>1513.419</v>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>flights</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Annual flight hours</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>1349.751</v>
-      </c>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GWP MODEL</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>GWP MODEL</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>GWP of full battery lifecycle</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>15660.03</v>
+      </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>kg CO2e</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GWP of full battery lifecycle</t>
+          <t>Ops GWP of battery annually</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>20122.838</v>
+        <v>36631.365</v>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
@@ -1958,11 +1958,11 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ops GWP of battery annually</t>
+          <t>Ops GWP of battery per flight</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>47102.821</v>
+        <v>9.677</v>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
@@ -1975,11 +1975,11 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ops GWP of battery per flight</t>
+          <t>Ops GWP of energy per flight</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10.612</v>
+        <v>18.22</v>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
@@ -1992,11 +1992,11 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ops GWP of energy per flight</t>
+          <t>Ops GWP total per flight</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>20.41</v>
+        <v>27.898</v>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
@@ -2009,11 +2009,11 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ops GWP total per flight</t>
+          <t>Ops GWP total per year</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>31.023</v>
+        <v>105598.568</v>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
@@ -2026,16 +2026,16 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ops GWP total per year</t>
+          <t>GWP fraction due energy</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>137693.781</v>
+        <v>65.31100000000001</v>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>kg CO2e</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -2043,11 +2043,11 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GWP fraction due energy</t>
+          <t>GWP fraction due battery</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>65.792</v>
+        <v>34.689</v>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
@@ -2057,42 +2057,42 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>GWP fraction due battery</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>34.208</v>
-      </c>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ECONOMIC MODEL - COST</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>ECONOMIC MODEL - COST</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Energy cost per trip</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>4.648</v>
+      </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Energy cost per trip</t>
+          <t>Navigation cost per trip</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>5.206</v>
+        <v>16.64</v>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
@@ -2105,11 +2105,11 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Navigation cost per trip</t>
+          <t>Crew cost per trip</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>17.402</v>
+        <v>12.446</v>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
@@ -2122,11 +2122,11 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Crew cost per trip</t>
+          <t>Wrap-rated maintenance cost per trip</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.614</v>
+        <v>13.194</v>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
@@ -2139,11 +2139,11 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Wrap-rated maintenance cost per trip</t>
+          <t>Battery unit cost</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10.035</v>
+        <v>14465.088</v>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
@@ -2156,11 +2156,11 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Battery unit cost</t>
+          <t>Battery maintenance cost per trip</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>18587.36</v>
+        <v>8.939</v>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
@@ -2173,11 +2173,11 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Battery maintenance cost per trip</t>
+          <t>Total maintenance cost per trip</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9.803000000000001</v>
+        <v>22.133</v>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
@@ -2190,11 +2190,11 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Total maintenance cost per trip</t>
+          <t>Cash operating cost per trip</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>19.838</v>
+        <v>55.867</v>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
@@ -2207,11 +2207,11 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cash operating cost per trip</t>
+          <t>Cost of ownership per trip</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>53.061</v>
+        <v>27.486</v>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
@@ -2224,11 +2224,11 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cost of ownership per trip</t>
+          <t>Direct operating cost per trip</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>24.554</v>
+        <v>83.354</v>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
@@ -2241,11 +2241,11 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Direct operating cost per trip</t>
+          <t>Indirect operating cost per trip</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>77.61499999999999</v>
+        <v>18.323</v>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
@@ -2258,11 +2258,11 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Indirect operating cost per trip</t>
+          <t>Total operating cost per trip</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>17.061</v>
+        <v>101.677</v>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
@@ -2275,16 +2275,16 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Total operating cost per trip</t>
+          <t>TOC per available seat per km</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>94.676</v>
+        <v>0.363</v>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>€</t>
+          <t>€/km</t>
         </is>
       </c>
     </row>
@@ -2292,56 +2292,56 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TOC per available seat per km</t>
+          <t>TOC per available seat per min</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.338</v>
+        <v>1.06</v>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>€/km</t>
+          <t>€/min</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>TOC per available seat per min</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>1.297</v>
-      </c>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>ECONOMIC MODEL - REVENUE</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>€/min</t>
-        </is>
-      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ECONOMIC MODEL - REVENUE</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ticket price per pax per trip</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>138.6</v>
+      </c>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>€</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ticket price per pax per trip</t>
+          <t>Revenue per trip</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>138.6</v>
+        <v>376.992</v>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
@@ -2351,62 +2351,45 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Revenue per trip</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>376.992</v>
-      </c>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>ECONOMIC MODEL - PROFIT</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Total profit per trip</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>275.315</v>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
         <is>
           <t>€</t>
         </is>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ECONOMIC MODEL - PROFIT</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Total profit per trip</t>
+          <t>Total profit per year</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>282.316</v>
+        <v>1042128.214</v>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
-        <is>
-          <t>€</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr"/>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Total profit per year</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>1253059.328</v>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
         <is>
           <t>€</t>
         </is>
@@ -2485,13 +2468,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.699</v>
+        <v>7.753</v>
       </c>
       <c r="C2" t="n">
         <v>64.235</v>
       </c>
       <c r="D2" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>1.183</v>
@@ -2519,13 +2502,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.518</v>
+        <v>7.572</v>
       </c>
       <c r="C3" t="n">
         <v>64.235</v>
       </c>
       <c r="D3" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E3" t="n">
         <v>2.366</v>
@@ -2553,13 +2536,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.43</v>
+        <v>7.487</v>
       </c>
       <c r="C4" t="n">
         <v>50.909</v>
       </c>
       <c r="D4" t="n">
-        <v>8.901999999999999</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="E4" t="n">
         <v>0.588</v>
@@ -2587,13 +2570,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.424</v>
+        <v>7.478</v>
       </c>
       <c r="C5" t="n">
         <v>64.235</v>
       </c>
       <c r="D5" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E5" t="n">
         <v>2.821</v>
@@ -2621,13 +2604,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.031</v>
+        <v>7.075</v>
       </c>
       <c r="C6" t="n">
         <v>105</v>
       </c>
       <c r="D6" t="n">
-        <v>7.083</v>
+        <v>7.217</v>
       </c>
       <c r="E6" t="n">
         <v>1.456</v>
@@ -2651,69 +2634,69 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Electric Vehicle (26%)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.999</v>
+        <v>7.012</v>
       </c>
       <c r="C7" t="n">
-        <v>285.957</v>
+        <v>64.235</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>7.762</v>
       </c>
       <c r="G7" t="n">
-        <v>-9955.456</v>
+        <v>12089.35</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>7.061</v>
       </c>
       <c r="I7" t="n">
-        <v>-43.994</v>
+        <v>7.371</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>4.659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Electric Vehicle (26%)</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.958</v>
+        <v>6.999</v>
       </c>
       <c r="C8" t="n">
-        <v>64.235</v>
+        <v>285.957</v>
       </c>
       <c r="D8" t="n">
-        <v>8.454000000000001</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>7.762</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>12089.35</v>
+        <v>-9955.456</v>
       </c>
       <c r="H8" t="n">
-        <v>7.061</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>7.371</v>
+        <v>-43.994</v>
       </c>
       <c r="J8" t="n">
-        <v>4.659</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2723,13 +2706,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.773</v>
+        <v>6.83</v>
       </c>
       <c r="C9" t="n">
         <v>50.909</v>
       </c>
       <c r="D9" t="n">
-        <v>8.901999999999999</v>
+        <v>9.074999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>1.008</v>
@@ -2757,13 +2740,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.695</v>
+        <v>6.739</v>
       </c>
       <c r="C10" t="n">
         <v>105</v>
       </c>
       <c r="D10" t="n">
-        <v>7.083</v>
+        <v>7.217</v>
       </c>
       <c r="E10" t="n">
         <v>2.464</v>
@@ -2791,13 +2774,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6.658</v>
+        <v>6.713</v>
       </c>
       <c r="C11" t="n">
         <v>64.235</v>
       </c>
       <c r="D11" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>5.915</v>
@@ -2825,13 +2808,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.28</v>
+        <v>6.335</v>
       </c>
       <c r="C12" t="n">
         <v>64.235</v>
       </c>
       <c r="D12" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>9.009</v>
@@ -2859,13 +2842,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.885</v>
+        <v>5.94</v>
       </c>
       <c r="C13" t="n">
         <v>64.235</v>
       </c>
       <c r="D13" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>10.92</v>
@@ -2893,13 +2876,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.788</v>
+        <v>5.842</v>
       </c>
       <c r="C14" t="n">
         <v>64.235</v>
       </c>
       <c r="D14" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E14" t="n">
         <v>11.648</v>
@@ -2927,31 +2910,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.398</v>
+        <v>5.498</v>
       </c>
       <c r="C15" t="n">
-        <v>18.246</v>
+        <v>23.989</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>11.405</v>
+        <v>10.256</v>
       </c>
       <c r="F15" t="n">
-        <v>4.391</v>
+        <v>4.956</v>
       </c>
       <c r="G15" t="n">
-        <v>19800.963</v>
+        <v>17676.225</v>
       </c>
       <c r="H15" t="n">
-        <v>6.033</v>
+        <v>6.316</v>
       </c>
       <c r="I15" t="n">
-        <v>34.807</v>
+        <v>37.381</v>
       </c>
       <c r="J15" t="n">
-        <v>1.806</v>
+        <v>1.538</v>
       </c>
     </row>
     <row r="16">
@@ -2961,13 +2944,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.248</v>
+        <v>5.303</v>
       </c>
       <c r="C16" t="n">
         <v>64.235</v>
       </c>
       <c r="D16" t="n">
-        <v>8.454000000000001</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>14.287</v>
@@ -2995,13 +2978,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.109</v>
+        <v>3.135</v>
       </c>
       <c r="C17" t="n">
         <v>179.595</v>
       </c>
       <c r="D17" t="n">
-        <v>4.576</v>
+        <v>4.654</v>
       </c>
       <c r="E17" t="n">
         <v>14.553</v>
@@ -3029,13 +3012,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.192</v>
+        <v>2.218</v>
       </c>
       <c r="C18" t="n">
         <v>179.595</v>
       </c>
       <c r="D18" t="n">
-        <v>4.576</v>
+        <v>4.654</v>
       </c>
       <c r="E18" t="n">
         <v>18.302</v>
